--- a/Promedios 10Hz.xlsx
+++ b/Promedios 10Hz.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyecto IMU´S PIIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149FD4C3-E8CD-4EF9-A471-A3B107B73D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F50FB8-AFFC-4C84-9AB9-91F2356F4FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1592F845-C67A-499F-9A34-82F3E9823049}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{1592F845-C67A-499F-9A34-82F3E9823049}"/>
   </bookViews>
   <sheets>
-    <sheet name="Eje X+" sheetId="3" r:id="rId1"/>
-    <sheet name="Eje X-" sheetId="2" r:id="rId2"/>
-    <sheet name="Eje Y+" sheetId="5" r:id="rId3"/>
-    <sheet name="Eje Y-" sheetId="4" r:id="rId4"/>
-    <sheet name="Eje Z+" sheetId="6" r:id="rId5"/>
-    <sheet name="Eje Z- " sheetId="1" r:id="rId6"/>
+    <sheet name="Eje +X" sheetId="3" r:id="rId1"/>
+    <sheet name="Eje -X" sheetId="2" r:id="rId2"/>
+    <sheet name="Eje +Y" sheetId="5" r:id="rId3"/>
+    <sheet name="Eje -Y" sheetId="4" r:id="rId4"/>
+    <sheet name="Eje +Z" sheetId="6" r:id="rId5"/>
+    <sheet name="Eje -Z " sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="20">
   <si>
     <t>Tiempo (s)</t>
   </si>
@@ -67,34 +67,52 @@
     <t>Gyr γ (rad/s)</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Se calculó la media aparatir de los 2 segundos (despues de 20 muestras)</t>
   </si>
   <si>
-    <t>Eje X+</t>
+    <t>Media (+X)</t>
   </si>
   <si>
-    <t>Eje X-</t>
+    <t>Media (-X)</t>
   </si>
   <si>
-    <t>Eje Y+</t>
+    <t>Media (+Y)</t>
   </si>
   <si>
-    <t>Eje Y-</t>
+    <t>Media (-Y)</t>
   </si>
   <si>
-    <t>Eje Z+</t>
+    <t>Media (+Z)</t>
   </si>
   <si>
-    <t>Eje Z-</t>
+    <t>Media (-Z)</t>
   </si>
   <si>
-    <t>Se calculó la media aparatir de los 2 segundos (despues de 20 muestras)</t>
+    <t>Acc X</t>
+  </si>
+  <si>
+    <t>Acc Y</t>
+  </si>
+  <si>
+    <t>Acc Z</t>
+  </si>
+  <si>
+    <t>Gyr α</t>
+  </si>
+  <si>
+    <t>Gyr β</t>
+  </si>
+  <si>
+    <t>Gyr γ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="172" formatCode="0.0000000000000000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -165,16 +183,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,6 +530,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA0B498-7E13-440D-8291-9000250C052C}">
   <dimension ref="A1:N602"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="33.33203125" customWidth="1"/>
+    <col min="10" max="10" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
@@ -603,14 +629,14 @@
       <c r="G4">
         <v>-3.1307000000000001E-2</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
+      <c r="I4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -634,23 +660,23 @@
       <c r="G5">
         <v>-2.8711E-2</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>13</v>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -675,24 +701,29 @@
       <c r="G6">
         <v>-2.6572999999999999E-2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <f>AVERAGE(B22:B602)</f>
         <v>1.0423967951807243</v>
       </c>
-      <c r="J6">
-        <v>-0.955341631034483</v>
-      </c>
-      <c r="K6">
-        <v>1.0205714206896539</v>
-      </c>
-      <c r="L6">
-        <v>-0.97974134482758668</v>
-      </c>
-      <c r="M6">
-        <v>1.0427220587219364</v>
-      </c>
-      <c r="N6">
-        <v>-0.9907348812392428</v>
+      <c r="J6" s="5">
+        <f t="shared" ref="I6:N6" si="0">AVERAGE(C22:C602)</f>
+        <v>7.1989793459552552E-3</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="0"/>
+        <v>-8.2200877796901901E-3</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" si="0"/>
+        <v>-2.098810327022373E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <f t="shared" si="0"/>
+        <v>1.4313242685025809E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <f t="shared" si="0"/>
+        <v>-2.959962478485369E-2</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -787,7 +818,7 @@
         <v>-3.4361000000000003E-2</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -14416,10 +14447,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C18CB1-8E10-4669-B5E7-D537C0662EFA}">
-  <dimension ref="A1:I601"/>
+  <dimension ref="A1:N601"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14442,7 +14480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -14466,7 +14504,7 @@
       </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -14488,12 +14526,8 @@
       <c r="G3">
         <v>-2.9169E-2</v>
       </c>
-      <c r="I3" s="4">
-        <f>AVERAGE(B22:B601)</f>
-        <v>-0.955341631034483</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -14515,8 +14549,16 @@
       <c r="G4">
         <v>-2.9322000000000001E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -14538,8 +14580,26 @@
       <c r="G5">
         <v>-3.3445000000000003E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -14561,8 +14621,31 @@
       <c r="G6">
         <v>-2.9016E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="5">
+        <v>-0.955341631034483</v>
+      </c>
+      <c r="J6" s="5">
+        <f>AVERAGE(C22:C601)</f>
+        <v>3.0773063793103496E-2</v>
+      </c>
+      <c r="K6" s="5">
+        <f>AVERAGE(D22:D601)</f>
+        <v>3.8989232758620707E-2</v>
+      </c>
+      <c r="L6" s="5">
+        <f>AVERAGE(E22:E601)</f>
+        <v>-2.1489017241379318E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <f>AVERAGE(F22:F601)</f>
+        <v>1.5290315517241375E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <f>AVERAGE(G22:G601)</f>
+        <v>-2.9620896551724136E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -14585,7 +14668,7 @@
         <v>-2.6724999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -14608,7 +14691,7 @@
         <v>-2.7642E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -14631,7 +14714,7 @@
         <v>-2.7947E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -14653,8 +14736,11 @@
       <c r="G10">
         <v>-3.0391000000000001E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -14677,7 +14763,7 @@
         <v>-3.1460000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -14700,7 +14786,7 @@
         <v>-2.9016E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -14723,7 +14809,7 @@
         <v>-2.8863E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -14746,7 +14832,7 @@
         <v>-3.1918000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -14769,7 +14855,7 @@
         <v>-2.7947E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -28248,16 +28334,25 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I4:N4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C5703D-E4AF-4BEF-8CAF-2490306537C0}">
-  <dimension ref="A1:I601"/>
+  <dimension ref="A1:N601"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -28280,7 +28375,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -28303,7 +28398,7 @@
         <v>-2.9932E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -28325,12 +28420,8 @@
       <c r="G3">
         <v>-3.1001000000000001E-2</v>
       </c>
-      <c r="I3" s="4">
-        <f>AVERAGE(C22:C601)</f>
-        <v>1.0205714206896539</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -28352,8 +28443,16 @@
       <c r="G4">
         <v>-2.9627000000000001E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -28375,8 +28474,26 @@
       <c r="G5">
         <v>-3.1460000000000002E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -28398,8 +28515,31 @@
       <c r="G6">
         <v>-2.9474E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="5">
+        <f>AVERAGE(B22:B601)</f>
+        <v>5.0042124137931028E-2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1.0205714206896539</v>
+      </c>
+      <c r="K6" s="5">
+        <f>AVERAGE(D22:D601)</f>
+        <v>3.1983255172413787E-2</v>
+      </c>
+      <c r="L6" s="5">
+        <f>AVERAGE(E22:E601)</f>
+        <v>-2.2185991379310356E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <f>AVERAGE(F22:F601)</f>
+        <v>1.8134567241379296E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <f>AVERAGE(G22:G601)</f>
+        <v>-2.9854196551724131E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -28422,7 +28562,7 @@
         <v>-2.9322000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -28445,7 +28585,7 @@
         <v>-3.0085000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -28468,7 +28608,7 @@
         <v>-2.8253E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -28490,8 +28630,11 @@
       <c r="G10">
         <v>-2.4282000000000001E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -28514,7 +28657,7 @@
         <v>-2.7182999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -28537,7 +28680,7 @@
         <v>-3.5277000000000003E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -28560,7 +28703,7 @@
         <v>-3.2223000000000002E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -28583,7 +28726,7 @@
         <v>-3.2529000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -28606,7 +28749,7 @@
         <v>-2.8863E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -42085,16 +42228,27 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I4:N4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32DE5D8-99CF-4D0E-B59E-82C158F9F795}">
-  <dimension ref="A1:I601"/>
+  <dimension ref="A1:N601"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -42117,7 +42271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -42140,7 +42294,7 @@
         <v>-2.9932E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -42162,12 +42316,8 @@
       <c r="G3">
         <v>-2.9322000000000001E-2</v>
       </c>
-      <c r="I3" s="4">
-        <f>AVERAGE(C22:C601)</f>
-        <v>-0.97974134482758668</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -42189,8 +42339,16 @@
       <c r="G4">
         <v>-3.4208000000000002E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -42212,8 +42370,26 @@
       <c r="G5">
         <v>-2.7947E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -42235,8 +42411,31 @@
       <c r="G6">
         <v>-2.5045000000000001E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="5">
+        <f>AVERAGE(B22:B601)</f>
+        <v>4.3033139655172428E-2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>-0.97974134482758668</v>
+      </c>
+      <c r="K6" s="5">
+        <f>AVERAGE(D22:D601)</f>
+        <v>6.7364732758620635E-2</v>
+      </c>
+      <c r="L6" s="5">
+        <f>AVERAGE(E22:E601)</f>
+        <v>-2.1268122413793115E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <f>AVERAGE(F22:F601)</f>
+        <v>1.657865344827588E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <f>AVERAGE(G22:G601)</f>
+        <v>-2.9929236206896508E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -42259,7 +42458,7 @@
         <v>-2.9932E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -42282,7 +42481,7 @@
         <v>-2.8405E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -42305,7 +42504,7 @@
         <v>-3.1307000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -42327,8 +42526,11 @@
       <c r="G10">
         <v>-2.6572999999999999E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -42351,7 +42553,7 @@
         <v>-3.1918000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -42374,7 +42576,7 @@
         <v>-3.1154000000000001E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -42397,7 +42599,7 @@
         <v>-2.9780000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -42420,7 +42622,7 @@
         <v>-2.7489E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -42443,7 +42645,7 @@
         <v>-2.7793999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -55922,16 +56124,25 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I4:N4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3F309A-8D25-4099-A53B-7D9FBAEAB81A}">
-  <dimension ref="A1:I600"/>
+  <dimension ref="A1:N600"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -55954,7 +56165,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -55977,7 +56188,7 @@
         <v>-3.1918000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -55999,12 +56210,8 @@
       <c r="G3">
         <v>-3.0849000000000001E-2</v>
       </c>
-      <c r="I3" s="4">
-        <f>AVERAGE(D22:D600)</f>
-        <v>1.0427220587219364</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -56026,8 +56233,16 @@
       <c r="G4">
         <v>-2.7489E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -56049,8 +56264,26 @@
       <c r="G5">
         <v>-3.3750000000000002E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -56072,8 +56305,32 @@
       <c r="G6">
         <v>-2.8863E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="5">
+        <f t="shared" ref="I6:N6" si="0">AVERAGE(B22:B600)</f>
+        <v>5.4797590673575126E-2</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="0"/>
+        <v>3.1155540587219338E-2</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="0"/>
+        <v>1.0427220587219364</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" si="0"/>
+        <v>-2.2552412780656304E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <f t="shared" si="0"/>
+        <v>2.0176240069084611E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <f t="shared" si="0"/>
+        <v>-2.9534898100172728E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -56096,7 +56353,7 @@
         <v>-2.7793999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -56119,7 +56376,7 @@
         <v>-2.7793999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -56142,7 +56399,7 @@
         <v>-2.8863E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -56164,8 +56421,11 @@
       <c r="G10">
         <v>-2.9322000000000001E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -56188,7 +56448,7 @@
         <v>-2.8711E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -56211,7 +56471,7 @@
         <v>-2.81E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -56234,7 +56494,7 @@
         <v>-2.3824000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -56257,7 +56517,7 @@
         <v>-2.9474E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -56280,7 +56540,7 @@
         <v>-2.5503999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -69736,16 +69996,25 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I4:N4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0008540-6CA5-4DBC-B479-EA4DB2A0A320}">
-  <dimension ref="A1:I602"/>
+  <dimension ref="A1:N602"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -69768,7 +70037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -69791,7 +70060,7 @@
         <v>-3.1460000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -69813,12 +70082,8 @@
       <c r="G3">
         <v>-3.3139000000000002E-2</v>
       </c>
-      <c r="I3" s="4">
-        <f>AVERAGE(D22:D602)</f>
-        <v>-0.9907348812392428</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -69840,8 +70105,16 @@
       <c r="G4">
         <v>-3.2681000000000002E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -69863,8 +70136,26 @@
       <c r="G5">
         <v>-3.3139000000000002E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -69886,8 +70177,31 @@
       <c r="G6">
         <v>-3.0391000000000001E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="5">
+        <f>AVERAGE(B22:B602)</f>
+        <v>3.9058707401032684E-2</v>
+      </c>
+      <c r="J6" s="5">
+        <f>AVERAGE(C22:C602)</f>
+        <v>6.2804371772805555E-3</v>
+      </c>
+      <c r="K6" s="5">
+        <v>-0.9907348812392428</v>
+      </c>
+      <c r="L6" s="5">
+        <f>AVERAGE(E22:E602)</f>
+        <v>-2.1217581755593792E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <f>AVERAGE(F22:F602)</f>
+        <v>1.7739552495697062E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <f>AVERAGE(G22:G602)</f>
+        <v>-3.0965920826161814E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -69910,7 +70224,7 @@
         <v>-3.2070000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -69933,7 +70247,7 @@
         <v>-2.8558E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -69956,7 +70270,7 @@
         <v>-2.7489E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -69978,8 +70292,11 @@
       <c r="G10">
         <v>-3.0543000000000001E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -70002,7 +70319,7 @@
         <v>-2.6419999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -70025,7 +70342,7 @@
         <v>-2.9932E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -70048,7 +70365,7 @@
         <v>-3.4208000000000002E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -70071,7 +70388,7 @@
         <v>-3.0849000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -70094,7 +70411,7 @@
         <v>-3.2529000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -83596,6 +83913,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I4:N4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
